--- a/data/pharmacist.xlsx
+++ b/data/pharmacist.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="4"/>
+    <s:workbookView activeTab="15"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -11,9 +11,17 @@
     <s:sheet name="savePharImg" sheetId="3" r:id="rId3"/>
     <s:sheet name="getWorkState" sheetId="4" r:id="rId4"/>
     <s:sheet name="setPharWorkState" sheetId="5" r:id="rId5"/>
-    <s:sheet name="syncAppointmentInfo" sheetId="6" r:id="rId6"/>
-    <s:sheet name="getDrugInfoByName" sheetId="7" r:id="rId7"/>
-    <s:sheet name="getPasteList" sheetId="8" r:id="rId8"/>
+    <s:sheet name="getDataList" sheetId="6" r:id="rId6"/>
+    <s:sheet name="checkPwd" sheetId="7" r:id="rId7"/>
+    <s:sheet name="gethistoryDataList" sheetId="8" r:id="rId8"/>
+    <s:sheet name="noapproved" sheetId="9" r:id="rId9"/>
+    <s:sheet name="approved" sheetId="10" r:id="rId10"/>
+    <s:sheet name="getOfflineOrderInfo" sheetId="11" r:id="rId11"/>
+    <s:sheet name="getMedicationInter" sheetId="12" r:id="rId12"/>
+    <s:sheet name="getMedicationHistory" sheetId="13" r:id="rId13"/>
+    <s:sheet name="getChatVideo" sheetId="14" r:id="rId14"/>
+    <s:sheet name="syncAppointmentInfo" sheetId="15" r:id="rId15"/>
+    <s:sheet name="CloseAppointment" sheetId="16" r:id="rId16"/>
   </s:sheets>
   <s:definedNames/>
   <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>case_id</t>
   </si>
@@ -119,46 +127,136 @@
     <t>{'workstate':1}</t>
   </si>
   <si>
+    <t>getDataList</t>
+  </si>
+  <si>
+    <t>获取药师审方列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/Auditor/getDataList?order=asc&amp;start=2020-05-09&amp;end=2020-05-09&amp;shop=&amp;doctor=</t>
+  </si>
+  <si>
+    <t>{'length':10,'search':'','start':0,'page':1}</t>
+  </si>
+  <si>
+    <t>{"draw": "1"}</t>
+  </si>
+  <si>
+    <t>checkPwd</t>
+  </si>
+  <si>
+    <t>验证药师审核密码-验证成功</t>
+  </si>
+  <si>
+    <t>/PharmacistExamine/checkPwd</t>
+  </si>
+  <si>
+    <t>{'paddword':0}</t>
+  </si>
+  <si>
+    <t>gethistoryDataList</t>
+  </si>
+  <si>
+    <t>获取历史处方-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/Auditor/getDataList?order=desc&amp;start=2019-10-24&amp;end=2019-10-24&amp;member=&amp;shop=&amp;isauditor=1&amp;type=1</t>
+  </si>
+  <si>
+    <t>{"draw":'1'}</t>
+  </si>
+  <si>
+    <t>noapproved</t>
+  </si>
+  <si>
+    <t>获取药师待审核处方列表-获取成功</t>
+  </si>
+  <si>
+    <t>/PharmacistExamine/getDataList</t>
+  </si>
+  <si>
+    <t>{'length':10,'search':'','start': 0,'page': 1,'shopcode':'','shopname':'','ordercode':'' ,'patientname':'' ,'patientphone':'','state':0,'phar':'范珑生','startTime':'2020-01-09','endTime':'2020-05-09'}</t>
+  </si>
+  <si>
+    <t>approved</t>
+  </si>
+  <si>
+    <t>获取药师已审核处方列表-获取成功</t>
+  </si>
+  <si>
+    <t>{'length':10,'search':'','start': 0,'page': 1,'shopcode':'','shopname':'','ordercode':'' ,'patientname':'' ,'patientphone':'','state':3,'phar':'范珑生','startTime':'2020-01-09','endTime':'2020-05-09'}</t>
+  </si>
+  <si>
+    <t>getOfflineOrderInfo</t>
+  </si>
+  <si>
+    <t>获取处方详情-获取成功</t>
+  </si>
+  <si>
+    <t>/PharmacistExamine/getOfflineOrderInfo</t>
+  </si>
+  <si>
+    <t>{'ordercode':'00000002|20200226174049493'}</t>
+  </si>
+  <si>
+    <t>{"CODE":'0000'}</t>
+  </si>
+  <si>
+    <t>getMedicationInter</t>
+  </si>
+  <si>
+    <t>获取用药咨询列表（实时列表）-获取成功</t>
+  </si>
+  <si>
+    <t>/onlineConsultation/getMedicationInter</t>
+  </si>
+  <si>
+    <t>{'patient':'','type':0}</t>
+  </si>
+  <si>
+    <t>{"draw":0}</t>
+  </si>
+  <si>
+    <t>getMedicationHistory</t>
+  </si>
+  <si>
+    <t>{'patient':'','type':1,'starttime':'','endtime':''}</t>
+  </si>
+  <si>
+    <t>getChatVideo</t>
+  </si>
+  <si>
+    <t>获取用药咨询视频-获取成功</t>
+  </si>
+  <si>
+    <t>/OnlineConsultation/getChatVedio</t>
+  </si>
+  <si>
+    <t>{'roomId':128214312}</t>
+  </si>
+  <si>
     <t>syncAppointmentInfo</t>
   </si>
   <si>
-    <t>修改问诊的预约状态-修改成功</t>
-  </si>
-  <si>
-    <t>/Other</t>
-  </si>
-  <si>
-    <t>{"QueryType": "syncAppointmentInfo","Params": '{"GUID":"ae89bb67b1540687a496c1dd78dd6813"}',"UserGuid":"MTg2OTkwfEA5Yzg0MWM4ZThmNzdjY2FhYjAwZTg2MDY2MmZmNDNjM3xAN2E2ZmQ0ZmRkOWRjYTRlZGQ4NzRiNmUzNjEzNmExOGU-"}</t>
-  </si>
-  <si>
-    <t>{"result": "0000", "msg": "获取成功"}</t>
-  </si>
-  <si>
-    <t>getDrugInfoByName</t>
-  </si>
-  <si>
-    <t>搜索西药处方药品-获取成功</t>
-  </si>
-  <si>
-    <t>/Drug</t>
-  </si>
-  <si>
-    <t>{"QueryType": "getDrugInfoByName","Params": '{"UserGuid":"MTg2OTkwfEBjN.....","UpKindId":"ROMENS","DrugName":"amxl"}',"UserGuid": "MTg2OTkwfEA5Yzg0MWM4ZThmNzdjY2FhYjAwZTg2MDY2MmZmNDNjM3xAN2E2ZmQ0ZmRkOWRjYTRlZGQ4NzRiNmUzNjEzNmExOGU-"}</t>
-  </si>
-  <si>
-    <t>getPasteList</t>
-  </si>
-  <si>
-    <t>搜索膏方处方药-获取成功</t>
-  </si>
-  <si>
-    <t>/ComHandle/getPasteList</t>
-  </si>
-  <si>
-    <t>{"QueryType": "","Params": '{"search":""}',"UserGuid": "MTg2OTkwfEA5Yzg0MWM4ZThmNzdjY2FhYjAwZTg2MDY2MmZmNDNjM3xAN2E2ZmQ0ZmRkOWRjYTRlZGQ4NzRiNmUzNjEzNmExOGU-"}</t>
-  </si>
-  <si>
-    <t>{"status_code":200}</t>
+    <t>接听用药咨询视频-获取成功</t>
+  </si>
+  <si>
+    <t>/OnlineConsultation/syncAppointmentInfo</t>
+  </si>
+  <si>
+    <t>{'GUID':'4698efe242c7423a575880f8581a5b23'}</t>
+  </si>
+  <si>
+    <t>CloseAppointment</t>
+  </si>
+  <si>
+    <t>挂断用药咨询视频-挂断成功</t>
+  </si>
+  <si>
+    <t>/OnlineConsultation/CloseAppointment</t>
+  </si>
+  <si>
+    <t>{'GUID':'4698efe242c7423a575880f8581a5b23','TYPE':3,'PARID':'1b4d9966c512388fbb297afdd8fff86f','USERIMID':'xst_186990_15764236502_006'}</t>
   </si>
 </sst>
 </file>
@@ -579,6 +677,530 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="9.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="32.875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="149.25" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="41.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="39.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="16.875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="35.25" customWidth="1" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="28.875" customWidth="1" min="5" max="5"/>
+    <col width="19.75" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="38.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="42" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="38.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="42.875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -898,12 +1520,12 @@
   <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18.25" customWidth="1" min="2" max="2"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="6.875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="179.5" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="79.5" customWidth="1" min="5" max="5"/>
+    <col width="30.75" customWidth="1" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -948,7 +1570,7 @@
       <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G2" t="s">
@@ -960,6 +1582,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -973,12 +1596,12 @@
   <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="19.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="102.375" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1030,7 +1653,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1052,12 +1675,11 @@
   <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.75" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="21.625" customWidth="1" min="5" max="5"/>
-    <col width="157.375" customWidth="1" min="6" max="6"/>
-    <col width="19.75" customWidth="1" min="7" max="7"/>
+    <col width="26.875" customWidth="1" min="5" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" s="3">
@@ -1103,10 +1725,10 @@
         <v>43</v>
       </c>
       <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
         <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1114,5 +1736,81 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="32.875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="30" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="148.125" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/pharmacist.xlsx
+++ b/data/pharmacist.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="15"/>
+    <s:workbookView activeTab="7"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -1678,7 +1678,8 @@
     <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.75" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="26.875" customWidth="1" min="5" max="6"/>
+    <col width="26.875" customWidth="1" min="5" max="5"/>
+    <col width="33.375" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>

--- a/data/pharmacist.xlsx
+++ b/data/pharmacist.xlsx
@@ -1,35 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:workbookPr codeName="ThisWorkbook"/>
-  <s:bookViews>
-    <s:workbookView activeTab="7"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet name="Login" sheetId="1" r:id="rId1"/>
-    <s:sheet name="checkPharCompareFace" sheetId="2" r:id="rId2"/>
-    <s:sheet name="savePharImg" sheetId="3" r:id="rId3"/>
-    <s:sheet name="getWorkState" sheetId="4" r:id="rId4"/>
-    <s:sheet name="setPharWorkState" sheetId="5" r:id="rId5"/>
-    <s:sheet name="getDataList" sheetId="6" r:id="rId6"/>
-    <s:sheet name="checkPwd" sheetId="7" r:id="rId7"/>
-    <s:sheet name="gethistoryDataList" sheetId="8" r:id="rId8"/>
-    <s:sheet name="noapproved" sheetId="9" r:id="rId9"/>
-    <s:sheet name="approved" sheetId="10" r:id="rId10"/>
-    <s:sheet name="getOfflineOrderInfo" sheetId="11" r:id="rId11"/>
-    <s:sheet name="getMedicationInter" sheetId="12" r:id="rId12"/>
-    <s:sheet name="getMedicationHistory" sheetId="13" r:id="rId13"/>
-    <s:sheet name="getChatVideo" sheetId="14" r:id="rId14"/>
-    <s:sheet name="syncAppointmentInfo" sheetId="15" r:id="rId15"/>
-    <s:sheet name="CloseAppointment" sheetId="16" r:id="rId16"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
-</s:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F74FA8-5A58-447F-B661-FB1D64614DB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="checkPharCompareFace" sheetId="2" r:id="rId2"/>
+    <sheet name="savePharImg" sheetId="3" r:id="rId3"/>
+    <sheet name="getWorkState" sheetId="4" r:id="rId4"/>
+    <sheet name="setPharWorkState" sheetId="5" r:id="rId5"/>
+    <sheet name="getDataList" sheetId="6" r:id="rId6"/>
+    <sheet name="checkPwd" sheetId="7" r:id="rId7"/>
+    <sheet name="gethistoryDataList" sheetId="8" r:id="rId8"/>
+    <sheet name="noapproved" sheetId="9" r:id="rId9"/>
+    <sheet name="approved" sheetId="10" r:id="rId10"/>
+    <sheet name="getOfflineOrderInfo" sheetId="11" r:id="rId11"/>
+    <sheet name="getMedicationInter" sheetId="12" r:id="rId12"/>
+    <sheet name="getMedicationHistory" sheetId="13" r:id="rId13"/>
+    <sheet name="getChatVideo" sheetId="14" r:id="rId14"/>
+    <sheet name="syncAppointmentInfo" sheetId="15" r:id="rId15"/>
+    <sheet name="CloseAppointment" sheetId="16" r:id="rId16"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="76">
   <si>
     <t>case_id</t>
   </si>
@@ -70,7 +76,7 @@
     <t>/index/login</t>
   </si>
   <si>
-    <t>{'username':'125433697645','password':'000000'}</t>
+    <t>{'username':'#phar_user#','password':'000000'}</t>
   </si>
   <si>
     <t>{"result": "0000", "msg": "验证成功"}</t>
@@ -88,9 +94,6 @@
     <t>/admin/Auditor/checkPharCompareFace</t>
   </si>
   <si>
-    <t>{'username':'125433697645'}</t>
-  </si>
-  <si>
     <t>{"CODE": "0000"}</t>
   </si>
   <si>
@@ -258,32 +261,34 @@
   <si>
     <t>{'GUID':'4698efe242c7423a575880f8581a5b23','TYPE':3,'PARID':'1b4d9966c512388fbb297afdd8fff86f','USERIMID':'xst_186990_15764236502_006'}</t>
   </si>
+  <si>
+    <t>{'username':'#phar_user#'}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -314,26 +319,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" builtinId="0" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -599,24 +612,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="43.875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,8 +654,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -672,27 +681,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="9.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="32.875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="149.25" customWidth="1" min="6" max="6"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="149.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,56 +724,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="41.5" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,56 +796,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
         <v>54</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>55</v>
-      </c>
-      <c r="G2" t="s">
-        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="39.125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="16.875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,56 +868,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
         <v>59</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>60</v>
-      </c>
-      <c r="G2" t="s">
-        <v>61</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="37.125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="35.25" customWidth="1" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.25" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -943,57 +940,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="28.875" customWidth="1" min="5" max="5"/>
-    <col width="19.75" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,55 +1013,52 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
         <v>66</v>
       </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="38.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="42" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1093,57 +1084,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
         <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" t="s">
-        <v>71</v>
-      </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="38.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="42.875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1169,57 +1157,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
         <v>74</v>
       </c>
-      <c r="F2" t="s">
-        <v>75</v>
-      </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="22.375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="34.75" customWidth="1" min="5" max="5"/>
-    <col width="26" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1248,8 +1233,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -1265,39 +1250,36 @@
         <v>18</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12.25" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="27.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="105.25" customWidth="1" min="6" max="6"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="105.25" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,57 +1308,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="25.125" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="32.375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="5.25" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,54 +1384,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="35.875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="12.875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1478,57 +1454,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="79.5" customWidth="1" min="5" max="5"/>
-    <col width="30.75" customWidth="1" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="79.5" customWidth="1"/>
+    <col min="6" max="6" width="30.75" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,57 +1527,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" t="s">
         <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="28.75" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1633,57 +1603,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.75" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="26.875" customWidth="1" min="5" max="5"/>
-    <col width="33.375" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.875" customWidth="1"/>
+    <col min="6" max="6" width="33.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" s="3">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1709,56 +1676,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
         <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>44</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.75" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="32.875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="30" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="148.125" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="148.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1784,34 +1748,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>